--- a/data/output/业绩冲减表_20260622.xlsx
+++ b/data/output/业绩冲减表_20260622.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,110 +477,6 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>客户姓名</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TK000001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>广州天河店</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>双眼皮手术</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>14960</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2244</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1496</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>11220</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>RF000001</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ORD000024</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>赵丽丽</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TK000002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>上海浦东店</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>瘦脸针</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2520</v>
-      </c>
-      <c r="F3" t="n">
-        <v>378</v>
-      </c>
-      <c r="G3" t="n">
-        <v>252</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1890</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>RF000004</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ORD000014</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>孙倩倩</t>
         </is>
       </c>
     </row>
@@ -595,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,60 +529,6 @@
         <is>
           <t>净业绩冲减</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>上海浦东店</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D2" t="n">
-        <v>378</v>
-      </c>
-      <c r="E2" t="n">
-        <v>252</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>广州天河店</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>14960</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2244</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1496</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>11220</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,32 +560,6 @@
         <is>
           <t>净业绩冲减</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>双眼皮手术</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>14960</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11220</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>瘦脸针</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2520</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1890</v>
       </c>
     </row>
   </sheetData>
